--- a/business_surveys/034_urban_sustainability_awareness_survey--business_surveys.xlsx
+++ b/business_surveys/034_urban_sustainability_awareness_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_very'}</t>
+          <t>not_very</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very'}</t>
+          <t>Not Very</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'toronto'}</t>
+          <t>toronto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Toronto'}</t>
+          <t>Toronto</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'vancouver'}</t>
+          <t>vancouver</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Vancouver'}</t>
+          <t>Vancouver</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'montreal'}</t>
+          <t>montreal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Montreal'}</t>
+          <t>Montreal</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'cities'}</t>
+          <t>cities</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Cities'}</t>
+          <t>Cities</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'ngos'}</t>
+          <t>ngos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'NGOs'}</t>
+          <t>NGOs</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'schools'}</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Schools'}</t>
+          <t>Schools</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'esg_teams'}</t>
+          <t>esg_teams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'ESG Teams'}</t>
+          <t>ESG Teams</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'034_urban_sustainability_awareness_survey--business_surveys'}</t>
+          <t>034_urban_sustainability_awareness_survey--business_surveys</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': '034_urban_sustainability_awareness_survey--business_surveys'}</t>
+          <t>034 urban sustainability awareness survey--business surveys</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'business_surveys'}</t>
+          <t>business_surveys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Business Surveys'}</t>
+          <t>Business Surveys</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
